--- a/numerical-workflows/v2/framework/经济/模块产销表/22_外循环_章节任务.xlsx
+++ b/numerical-workflows/v2/framework/经济/模块产销表/22_外循环_章节任务.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资源汇总" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="机器明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机器明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'产销阅读'!$A$1:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资源汇总'!$A$1:$J$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'机器明细'!$A$1:$M$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'产销阅读'!$A$1:$J$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资源汇总'!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'机器明细'!$A$1:$M$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -202,8 +202,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_readable" displayName="T_readable" ref="A1:J10" headerRowCount="1">
-  <autoFilter ref="A1:J10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_readable" displayName="T_readable" ref="A1:J12" headerRowCount="1">
+  <autoFilter ref="A1:J12"/>
   <tableColumns count="10">
     <tableColumn id="1" name="系统"/>
     <tableColumn id="2" name="分组"/>
@@ -221,8 +221,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_resources" displayName="T_resources" ref="A1:J17" headerRowCount="1">
-  <autoFilter ref="A1:J17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_resources" displayName="T_resources" ref="A1:J22" headerRowCount="1">
+  <autoFilter ref="A1:J22"/>
   <tableColumns count="10">
     <tableColumn id="1" name="资源分类"/>
     <tableColumn id="2" name="资源/道具"/>
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_chapter_task" displayName="T_chapter_task" ref="A1:M28" headerRowCount="1">
-  <autoFilter ref="A1:M28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_chapter_task" displayName="T_chapter_task" ref="A1:M45" headerRowCount="1">
+  <autoFilter ref="A1:M45"/>
   <tableColumns count="13">
     <tableColumn id="1" name="分组"/>
     <tableColumn id="2" name="方向"/>
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -660,7 +660,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>产出:20；引用:7</t>
+          <t>产出:40；引用:4</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,11 @@
           <t>价值分布(钻石)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>产出:490.0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -680,7 +684,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>猎鹰金币(1) 合计x350000；限时旅券(111) 合计x40；合淬喷剂(13) 合计x35000；3级红宝石(81103) 合计x2；3级绿宝石(81403) 合计x2；3级黄宝石(81303) 合计x2；应急收容凭证(112) 合计x10；未知笔记(110) 合计x5；熔晶(103) 合计x1；蓝色装备宝箱(3021) 合计x1；另3项</t>
+          <t>旅券(106) 合计x21；限时旅券(111) 合计x21；收容凭证(107) 合计x30；熔晶(103) 合计x3；史诗能效自选箱(3017) 合计x10；指南材料自选箱(3027) 合计x35；稀有能效自选箱(3016) 合计x11；高阶记录盘(102) 合计x18；15级精品装备箱(2505) 合计x1；20级精品装备箱(2506) 合计x1；另10项</t>
         </is>
       </c>
     </row>
@@ -700,7 +704,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ChapterTasks.DropId 合计x200000024；元晶(2) 合计x100；中阶记录盘(101) 合计x10</t>
+          <t>ChapterTasks.DropId 合计x200000024</t>
         </is>
       </c>
     </row>
@@ -712,7 +716,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x20；正式:level/ChapterTasks.xlsx x4；正式:task/JottingsTask.xlsx + Drop_other.xlsx x3</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x40；正式:level/ChapterTasks.xlsx x4</t>
         </is>
       </c>
     </row>
@@ -724,7 +728,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>高敏感；需展开Drop/Reward；随机/引用</t>
+          <t>需展开Drop/Reward；随机/引用</t>
         </is>
       </c>
     </row>
@@ -757,7 +761,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
@@ -765,7 +769,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -778,18 +782,6 @@
       </c>
       <c r="E21" s="5" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>候选章节任务序章奖励</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -803,7 +795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -878,39 +870,35 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>候选章节任务序章奖励</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
+          <t>正式章节任务奖励</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>星海手札（序章，Jottings未配置）｜JottingsTask 11;12;13｜Task 1301;1302;1303</t>
+          <t>ChapterId 10000｜TaskIdList 10;11;12</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>候选章节任务序章奖励：元晶(2) x50 x2；候选章节任务序章奖励：中阶记录盘(101) x10</t>
+          <t>正式章节任务奖励：ChapterTasks.DropId x50000006</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>正式:task/JottingsTask.xlsx + Drop_other.xlsx</t>
+          <t>正式:level/ChapterTasks.xlsx:5</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>章节任务候选奖励，未计为正式产出</t>
+          <t>奖励包/配置引用，待 DropId/RewardId 展开</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>候选序章奖励；Jottings 未挂载，DropID 1030103 仅作待确认展示。；候选序章奖励；Jottings 未挂载，DropID 1030101 仅作待确认展示。；候选序章奖励；Jottings 未挂载，DropID 1030102 仅作待确认展示。</t>
+          <t>旧 ChapterTasks 链路保留为异常参考；当前正确章节任务链来自 task/Jottings。</t>
         </is>
       </c>
     </row>
@@ -928,7 +916,7 @@
       <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ChapterId 10000｜TaskIdList 10;11;12</t>
+          <t>ChapterId 10001｜TaskIdList 18;19;20</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr"/>
@@ -940,7 +928,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>正式:level/ChapterTasks.xlsx:5</t>
+          <t>正式:level/ChapterTasks.xlsx:6</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -968,7 +956,7 @@
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>ChapterId 10001｜TaskIdList 18;19;20</t>
+          <t>ChapterId 10002｜TaskIdList 21;22;23;24;25</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr"/>
@@ -980,7 +968,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>正式:level/ChapterTasks.xlsx:6</t>
+          <t>正式:level/ChapterTasks.xlsx:7</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1008,7 +996,7 @@
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>ChapterId 10002｜TaskIdList 21;22;23;24;25</t>
+          <t>ChapterId 10003｜TaskIdList 26;27;28;29;30</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr"/>
@@ -1020,7 +1008,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>正式:level/ChapterTasks.xlsx:7</t>
+          <t>正式:level/ChapterTasks.xlsx:8</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1042,35 +1030,39 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务奖励</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>ChapterId 10003｜TaskIdList 26;27;28;29;30</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
+          <t>星海手札（一）｜JottingsTask 21;22;23;24;25｜Task 1311;1312;1313;1314;1315;1316</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励：旅券(106) x3；正式章节任务阶段奖励：稀有能效自选箱(3016) x5；正式章节任务阶段奖励：限时旅券(111) x3；正式章节任务阶段奖励：高阶记录盘(102) x8</t>
+        </is>
+      </c>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>正式章节任务奖励：ChapterTasks.DropId x50000006</t>
-        </is>
-      </c>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>正式:level/ChapterTasks.xlsx:8</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx:5</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>奖励包/配置引用，待 DropId/RewardId 展开</t>
+          <t>章节任务阶段奖励展开</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>旧 ChapterTasks 链路保留为异常参考；当前正确章节任务链来自 task/Jottings。</t>
+          <t>DropID 1040202；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -1092,19 +1084,19 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>星海手札（一）｜JottingsTask 21;22;23;24;25｜Task 1311;1312;1313;1314;1315;1316</t>
+          <t>星海手札（七）｜JottingsTask 81;82;83;84;85;86;87;88;89;90｜Task 1371;1372;1373;1374;1375;1376;1377;1378;1388;1389;1390;1391</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励：未知笔记(110) x5；正式章节任务阶段奖励：熔晶(103) x1；正式章节任务阶段奖励：猎鹰金币(1) x50000；正式章节任务阶段奖励：限时旅券(111) x10；正式章节任务阶段奖励：高阶记录盘(102) x5</t>
+          <t>正式章节任务阶段奖励：4级宝石掉落箱(3013) x2；正式章节任务阶段奖励：40级高级装备箱(2510) x1；正式章节任务阶段奖励：传说能效自选箱(3018) x5；正式章节任务阶段奖励：收容凭证(107) x10；正式章节任务阶段奖励：旅券(106) x3；正式章节任务阶段奖励：熔晶(103) x1；正式章节任务阶段奖励：限时旅券(111) x3</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>正式:task/Jottings.xlsx + Drop_other.xlsx:5</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx:11</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1114,7 +1106,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040202；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040208；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1128,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46｜Task 1331;1332;1333;1334;1335;1336;1337;1338</t>
+          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46;47｜Task 1331;1332;1333;1334;1335;1336;1337;1338;1339</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励：3级黄宝石(81303) x2；正式章节任务阶段奖励：合淬喷剂(13) x15000；正式章节任务阶段奖励：猎鹰金币(1) x100000；正式章节任务阶段奖励：限时旅券(111) x10；正式章节任务阶段奖励：随机稀有装备(2502) x4</t>
+          <t>正式章节任务阶段奖励：20级精品装备箱(2506) x1；正式章节任务阶段奖励：指南材料自选箱(3027) x15；正式章节任务阶段奖励：旅券(106) x3；正式章节任务阶段奖励：熔晶(103) x1；正式章节任务阶段奖励：简式设备图纸(3028) x12；正式章节任务阶段奖励：限时旅券(111) x3</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
@@ -1185,7 +1177,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励：3级红宝石(81103) x2；正式章节任务阶段奖励：猎鹰金币(1) x100000；正式章节任务阶段奖励：蓝色装备宝箱(3021) x1；正式章节任务阶段奖励：限时旅券(111) x10</t>
+          <t>正式章节任务阶段奖励：15级精品装备箱(2505) x1；正式章节任务阶段奖励：旅券(106) x3；正式章节任务阶段奖励：稀有能效自选箱(3016) x6；正式章节任务阶段奖励：限时旅券(111) x3；正式章节任务阶段奖励：高阶记录盘(102) x10</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
@@ -1224,34 +1216,122 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56｜Task 1341;1342;1343;1344;1345;1346;1347;1348</t>
+          <t>星海手札（五）｜JottingsTask 61;62;63;64;65;66;67;68;69;26｜Task 1351;1352;1353;1354;1355;1356;1357;1358;1381;1382;1383;1401</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励：3级绿宝石(81403) x2；正式章节任务阶段奖励：合淬喷剂(13) x20000；正式章节任务阶段奖励：应急收容凭证(112) x10；正式章节任务阶段奖励：猎鹰金币(1) x100000；正式章节任务阶段奖励：限时旅券(111) x10；正式章节任务阶段奖励：随机史诗装备(2503) x1</t>
+          <t>正式章节任务阶段奖励：2级宝石掉落箱(3011) x2；正式章节任务阶段奖励：30级精品装备箱(2508) x1；正式章节任务阶段奖励：收容凭证(107) x10；正式章节任务阶段奖励：旅券(106) x3；正式章节任务阶段奖励：未知笔记(110) x5；正式章节任务阶段奖励：熔晶(103) x1；正式章节任务阶段奖励：限时旅券(111) x3</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr">
         <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx:9</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040206；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>主线</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（六）｜JottingsTask 71;72;73;74;75;76;77;78;79;80｜Task 1361;1362;1363;1364;1365;1366;1367;1368;1384;1385;1386;1387</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励：3级宝石掉落箱(3012) x2；正式章节任务阶段奖励：35级高级装备箱(2509) x1；正式章节任务阶段奖励：史诗能效自选箱(3017) x5；正式章节任务阶段奖励：收容凭证(107) x10；正式章节任务阶段奖励：旅券(106) x3；正式章节任务阶段奖励：限时旅券(111) x3</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx:10</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040207；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>主线</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56;57;58｜Task 1341;1342;1343;1344;1345;1346;1347;1348;1349;1350</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励：25级精品装备箱(2507) x1；正式章节任务阶段奖励：史诗能效自选箱(3017) x5；正式章节任务阶段奖励：指南材料自选箱(3027) x20；正式章节任务阶段奖励：旅券(106) x3；正式章节任务阶段奖励：限时旅券(111) x3</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
           <t>正式:task/Jottings.xlsx + Drop_other.xlsx:8</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>章节任务阶段奖励展开</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J10"/>
+  <autoFilter ref="A1:J12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1265,7 +1345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1340,12 +1420,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>合淬喷剂</t>
+          <t>熔晶</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -1354,11 +1434,11 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1368,12 +1448,12 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励 x2</t>
+          <t>正式章节任务阶段奖励 x3</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x2</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x3</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -1390,12 +1470,12 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>未知笔记</t>
+          <t>史诗能效自选箱</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -1404,26 +1484,26 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励</t>
+          <t>正式章节任务阶段奖励 x2</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x2</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -1440,12 +1520,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>熔晶</t>
+          <t>稀有能效自选箱</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -1454,26 +1534,26 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励</t>
+          <t>正式章节任务阶段奖励 x2</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x2</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -1504,11 +1584,11 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1518,12 +1598,12 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励</t>
+          <t>正式章节任务阶段奖励 x2</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x2</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -1535,17 +1615,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>养成材料</t>
+          <t>其他资源</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3级红宝石</t>
+          <t>传说能效自选箱</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>81103</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -1558,12 +1638,12 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1585,17 +1665,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>养成材料</t>
+          <t>其他资源</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>3级绿宝石</t>
+          <t>未知笔记</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>81403</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1608,7 +1688,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1635,17 +1715,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>养成材料</t>
+          <t>其他资源</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>3级黄宝石</t>
+          <t>简式设备图纸</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>81303</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1658,7 +1738,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1690,12 +1770,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>蓝色装备宝箱</t>
+          <t>指南材料自选箱</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1704,11 +1784,11 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1718,12 +1798,12 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励</t>
+          <t>正式章节任务阶段奖励 x2</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x2</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1740,12 +1820,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>15级精品装备箱</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1790,12 +1870,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>随机稀有装备</t>
+          <t>20级精品装备箱</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1808,7 +1888,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1835,32 +1915,32 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>基础货币/体力</t>
+          <t>养成材料</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>猎鹰金币</t>
+          <t>25级精品装备箱</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
+          <t>2507</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>产出</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>350000</t>
-        </is>
-      </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1868,12 +1948,12 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励 x4</t>
+          <t>正式章节任务阶段奖励</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x4</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1885,32 +1965,32 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>基础货币/体力</t>
+          <t>养成材料</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>2级宝石掉落箱</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
+          <t>3011</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1918,43 +1998,47 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>候选章节任务序章奖励 x2</t>
+          <t>正式章节任务阶段奖励</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>正式:task/JottingsTask.xlsx + Drop_other.xlsx x2</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>高敏感；需展开Drop/Reward；随机/引用</t>
+          <t>随机/引用</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奖励包/配置引用</t>
+          <t>养成材料</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ChapterTasks.DropId</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>引用</t>
+          <t>30级精品装备箱</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>2508</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>200000024</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1964,39 +2048,39 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务奖励 x4</t>
+          <t>正式章节任务阶段奖励</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>正式:level/ChapterTasks.xlsx x4</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>需展开Drop/Reward；随机/引用</t>
+          <t>随机/引用</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奖励包/配置引用</t>
+          <t>养成材料</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>中阶记录盘</t>
+          <t>35级高级装备箱</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>引用</t>
+          <t>2509</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
@@ -2004,7 +2088,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -2014,34 +2098,34 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>候选章节任务序章奖励</t>
+          <t>正式章节任务阶段奖励</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>正式:task/JottingsTask.xlsx + Drop_other.xlsx</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>需展开Drop/Reward；随机/引用</t>
+          <t>随机/引用</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>抽卡/角色获取</t>
+          <t>养成材料</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>限时旅券</t>
+          <t>3级宝石掉落箱</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -2050,11 +2134,11 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2064,12 +2148,12 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务阶段奖励 x4</t>
+          <t>正式章节任务阶段奖励</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x4</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -2081,17 +2165,17 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>抽卡/角色获取</t>
+          <t>养成材料</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>应急收容凭证</t>
+          <t>40级高级装备箱</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -2104,7 +2188,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2128,8 +2212,254 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>养成材料</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>4级宝石掉落箱</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>3013</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>随机/引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>奖励包/配置引用</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>ChapterTasks.DropId</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>引用</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>200000024</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务奖励 x4</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>正式:level/ChapterTasks.xlsx x4</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>需展开Drop/Reward；随机/引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>抽卡/角色获取</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>旅券</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励 x7</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x7</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>随机/引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>抽卡/角色获取</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>限时旅券</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励 x7</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x7</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>随机/引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>抽卡/角色获取</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>收容凭证</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励 x3</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx x3</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>随机/引用</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J17"/>
+  <autoFilter ref="A1:J22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2143,7 +2473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2231,7 +2561,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>候选章节任务序章奖励</t>
+          <t>正式章节任务奖励</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -2241,46 +2571,44 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>中阶记录盘</t>
+          <t>ChapterTasks.DropId</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>10</v>
+        <v>50000006</v>
       </c>
       <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
+      <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>星海手札（序章，Jottings未配置）｜JottingsTask 11;12;13｜Task 1301;1302;1303</t>
+          <t>ChapterId 10000｜TaskIdList 10;11;12</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>正式:task/JottingsTask.xlsx + Drop_other.xlsx</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr"/>
+          <t>正式:level/ChapterTasks.xlsx</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>章节任务候选奖励，未计为正式产出</t>
+          <t>奖励包/配置引用，待 DropId/RewardId 展开</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>候选序章奖励；Jottings 未挂载，DropID 1030103 仅作待确认展示。</t>
+          <t>旧 ChapterTasks 链路保留为异常参考；当前正确章节任务链来自 task/Jottings。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>候选章节任务序章奖励</t>
+          <t>正式章节任务奖励</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -2290,46 +2618,44 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>ChapterTasks.DropId</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>50</v>
+        <v>50000006</v>
       </c>
       <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
+      <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>星海手札（序章，Jottings未配置）｜JottingsTask 11;12;13｜Task 1301;1302;1303</t>
+          <t>ChapterId 10001｜TaskIdList 18;19;20</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>正式:task/JottingsTask.xlsx + Drop_other.xlsx</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr"/>
+          <t>正式:level/ChapterTasks.xlsx</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>章节任务候选奖励，未计为正式产出</t>
+          <t>奖励包/配置引用，待 DropId/RewardId 展开</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>候选序章奖励；Jottings 未挂载，DropID 1030101 仅作待确认展示。</t>
+          <t>旧 ChapterTasks 链路保留为异常参考；当前正确章节任务链来自 task/Jottings。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>候选章节任务序章奖励</t>
+          <t>正式章节任务奖励</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -2339,39 +2665,37 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>ChapterTasks.DropId</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>50</v>
+        <v>50000006</v>
       </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>星海手札（序章，Jottings未配置）｜JottingsTask 11;12;13｜Task 1301;1302;1303</t>
+          <t>ChapterId 10002｜TaskIdList 21;22;23;24;25</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>正式:task/JottingsTask.xlsx + Drop_other.xlsx</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
+          <t>正式:level/ChapterTasks.xlsx</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>章节任务候选奖励，未计为正式产出</t>
+          <t>奖励包/配置引用，待 DropId/RewardId 展开</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>候选序章奖励；Jottings 未挂载，DropID 1030102 仅作待确认展示。</t>
+          <t>旧 ChapterTasks 链路保留为异常参考；当前正确章节任务链来自 task/Jottings。</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2724,7 @@
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>ChapterId 10000｜TaskIdList 10;11;12</t>
+          <t>ChapterId 10003｜TaskIdList 26;27;28;29;30</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -2409,7 +2733,7 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
@@ -2425,141 +2749,155 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务奖励</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>引用</t>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ChapterTasks.DropId</t>
+          <t>旅券</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>50000006</v>
+        <v>3</v>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>ChapterId 10001｜TaskIdList 18;19;20</t>
+          <t>星海手札（一）｜JottingsTask 21;22;23;24;25｜Task 1311;1312;1313;1314;1315;1316</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>正式:level/ChapterTasks.xlsx</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>奖励包/配置引用，待 DropId/RewardId 展开</t>
+          <t>章节任务阶段奖励展开</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>旧 ChapterTasks 链路保留为异常参考；当前正确章节任务链来自 task/Jottings。</t>
+          <t>DropID 1040202；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务奖励</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>引用</t>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ChapterTasks.DropId</t>
+          <t>稀有能效自选箱</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>50000006</v>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>75</v>
+      </c>
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>ChapterId 10002｜TaskIdList 21;22;23;24;25</t>
+          <t>星海手札（一）｜JottingsTask 21;22;23;24;25｜Task 1311;1312;1313;1314;1315;1316</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>正式:level/ChapterTasks.xlsx</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>奖励包/配置引用，待 DropId/RewardId 展开</t>
+          <t>章节任务阶段奖励展开</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>旧 ChapterTasks 链路保留为异常参考；当前正确章节任务链来自 task/Jottings。</t>
+          <t>DropID 1040202；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>正式章节任务奖励</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>引用</t>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ChapterTasks.DropId</t>
+          <t>限时旅券</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>50000006</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>ChapterId 10003｜TaskIdList 26;27;28;29;30</t>
+          <t>星海手札（一）｜JottingsTask 21;22;23;24;25｜Task 1311;1312;1313;1314;1315;1316</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>正式:level/ChapterTasks.xlsx</t>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>奖励包/配置引用，待 DropId/RewardId 展开</t>
+          <t>章节任务阶段奖励展开</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>旧 ChapterTasks 链路保留为异常参考；当前正确章节任务链来自 task/Jottings。</t>
+          <t>DropID 1040202；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -2576,11 +2914,11 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>未知笔记</t>
+          <t>高阶记录盘</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr"/>
@@ -2627,11 +2965,11 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>熔晶</t>
+          <t>4级宝石掉落箱</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr"/>
@@ -2643,7 +2981,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>星海手札（一）｜JottingsTask 21;22;23;24;25｜Task 1311;1312;1313;1314;1315;1316</t>
+          <t>星海手札（七）｜JottingsTask 81;82;83;84;85;86;87;88;89;90｜Task 1371;1372;1373;1374;1375;1376;1377;1378;1388;1389;1390;1391</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -2652,7 +2990,7 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
@@ -2661,7 +2999,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040202；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040208；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -2678,11 +3016,11 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>猎鹰金币</t>
+          <t>40级高级装备箱</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr"/>
@@ -2694,7 +3032,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>星海手札（一）｜JottingsTask 21;22;23;24;25｜Task 1311;1312;1313;1314;1315;1316</t>
+          <t>星海手札（七）｜JottingsTask 81;82;83;84;85;86;87;88;89;90｜Task 1371;1372;1373;1374;1375;1376;1377;1378;1388;1389;1390;1391</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -2703,7 +3041,7 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
@@ -2712,7 +3050,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040202；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040208；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -2729,13 +3067,15 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>限时旅券</t>
+          <t>传说能效自选箱</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>125</v>
+      </c>
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
@@ -2745,7 +3085,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>星海手札（一）｜JottingsTask 21;22;23;24;25｜Task 1311;1312;1313;1314;1315;1316</t>
+          <t>星海手札（七）｜JottingsTask 81;82;83;84;85;86;87;88;89;90｜Task 1371;1372;1373;1374;1375;1376;1377;1378;1388;1389;1390;1391</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -2754,7 +3094,7 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
@@ -2763,7 +3103,7 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040202；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040208；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -2780,11 +3120,11 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>高阶记录盘</t>
+          <t>收容凭证</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
@@ -2796,7 +3136,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>星海手札（一）｜JottingsTask 21;22;23;24;25｜Task 1311;1312;1313;1314;1315;1316</t>
+          <t>星海手札（七）｜JottingsTask 81;82;83;84;85;86;87;88;89;90｜Task 1371;1372;1373;1374;1375;1376;1377;1378;1388;1389;1390;1391</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -2805,7 +3145,7 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
@@ -2814,7 +3154,7 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040202；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040208；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -2831,11 +3171,11 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>3级黄宝石</t>
+          <t>旅券</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
@@ -2847,7 +3187,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46｜Task 1331;1332;1333;1334;1335;1336;1337;1338</t>
+          <t>星海手札（七）｜JottingsTask 81;82;83;84;85;86;87;88;89;90｜Task 1371;1372;1373;1374;1375;1376;1377;1378;1388;1389;1390;1391</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -2856,7 +3196,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
@@ -2865,7 +3205,7 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040204；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040208；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -2882,11 +3222,11 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>合淬喷剂</t>
+          <t>熔晶</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>15000</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr"/>
@@ -2898,7 +3238,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46｜Task 1331;1332;1333;1334;1335;1336;1337;1338</t>
+          <t>星海手札（七）｜JottingsTask 81;82;83;84;85;86;87;88;89;90｜Task 1371;1372;1373;1374;1375;1376;1377;1378;1388;1389;1390;1391</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -2907,7 +3247,7 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
@@ -2916,7 +3256,7 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040204；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040208；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -2933,11 +3273,11 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>猎鹰金币</t>
+          <t>限时旅券</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>100000</v>
+        <v>3</v>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
@@ -2949,7 +3289,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46｜Task 1331;1332;1333;1334;1335;1336;1337;1338</t>
+          <t>星海手札（七）｜JottingsTask 81;82;83;84;85;86;87;88;89;90｜Task 1371;1372;1373;1374;1375;1376;1377;1378;1388;1389;1390;1391</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -2958,7 +3298,7 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
@@ -2967,7 +3307,7 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040204；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040208；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -2984,11 +3324,11 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>限时旅券</t>
+          <t>20级精品装备箱</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr"/>
@@ -3000,7 +3340,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46｜Task 1331;1332;1333;1334;1335;1336;1337;1338</t>
+          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46;47｜Task 1331;1332;1333;1334;1335;1336;1337;1338;1339</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -3035,11 +3375,11 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>随机稀有装备</t>
+          <t>指南材料自选箱</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr"/>
@@ -3051,7 +3391,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46｜Task 1331;1332;1333;1334;1335;1336;1337;1338</t>
+          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46;47｜Task 1331;1332;1333;1334;1335;1336;1337;1338;1339</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -3086,11 +3426,11 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>3级红宝石</t>
+          <t>旅券</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr"/>
@@ -3102,7 +3442,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>星海手札（二）｜JottingsTask 31;32;33;34;35;36｜Task 1321;1322;1323;1324;1325;1326;1327;1328</t>
+          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46;47｜Task 1331;1332;1333;1334;1335;1336;1337;1338;1339</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -3111,7 +3451,7 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
@@ -3120,7 +3460,7 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040203；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040204；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -3137,11 +3477,11 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>猎鹰金币</t>
+          <t>熔晶</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr"/>
@@ -3153,7 +3493,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>星海手札（二）｜JottingsTask 31;32;33;34;35;36｜Task 1321;1322;1323;1324;1325;1326;1327;1328</t>
+          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46;47｜Task 1331;1332;1333;1334;1335;1336;1337;1338;1339</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -3162,7 +3502,7 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
@@ -3171,7 +3511,7 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040203；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040204；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -3188,11 +3528,11 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蓝色装备宝箱</t>
+          <t>简式设备图纸</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="5" t="inlineStr"/>
@@ -3204,7 +3544,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>星海手札（二）｜JottingsTask 31;32;33;34;35;36｜Task 1321;1322;1323;1324;1325;1326;1327;1328</t>
+          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46;47｜Task 1331;1332;1333;1334;1335;1336;1337;1338;1339</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -3213,7 +3553,7 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
@@ -3222,7 +3562,7 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040203；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040204；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3583,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="5" t="inlineStr"/>
@@ -3255,7 +3595,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>星海手札（二）｜JottingsTask 31;32;33;34;35;36｜Task 1321;1322;1323;1324;1325;1326;1327;1328</t>
+          <t>星海手札（三）｜JottingsTask 41;42;43;44;45;46;47｜Task 1331;1332;1333;1334;1335;1336;1337;1338;1339</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -3264,7 +3604,7 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
@@ -3273,7 +3613,7 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040203；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040204；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -3290,11 +3630,11 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>3级绿宝石</t>
+          <t>15级精品装备箱</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr"/>
@@ -3306,7 +3646,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56｜Task 1341;1342;1343;1344;1345;1346;1347;1348</t>
+          <t>星海手札（二）｜JottingsTask 31;32;33;34;35;36｜Task 1321;1322;1323;1324;1325;1326;1327;1328</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -3315,7 +3655,7 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
@@ -3324,7 +3664,7 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040203；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -3341,11 +3681,11 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>合淬喷剂</t>
+          <t>旅券</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>20000</v>
+        <v>3</v>
       </c>
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr"/>
@@ -3357,7 +3697,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56｜Task 1341;1342;1343;1344;1345;1346;1347;1348</t>
+          <t>星海手札（二）｜JottingsTask 31;32;33;34;35;36｜Task 1321;1322;1323;1324;1325;1326;1327;1328</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -3366,7 +3706,7 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
@@ -3375,7 +3715,7 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040203；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -3392,13 +3732,15 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>应急收容凭证</t>
+          <t>稀有能效自选箱</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>90</v>
+      </c>
       <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
@@ -3408,7 +3750,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56｜Task 1341;1342;1343;1344;1345;1346;1347;1348</t>
+          <t>星海手札（二）｜JottingsTask 31;32;33;34;35;36｜Task 1321;1322;1323;1324;1325;1326;1327;1328</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -3417,7 +3759,7 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
@@ -3426,7 +3768,7 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040203；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -3443,11 +3785,11 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>猎鹰金币</t>
+          <t>限时旅券</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>100000</v>
+        <v>3</v>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr"/>
@@ -3459,7 +3801,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56｜Task 1341;1342;1343;1344;1345;1346;1347;1348</t>
+          <t>星海手札（二）｜JottingsTask 31;32;33;34;35;36｜Task 1321;1322;1323;1324;1325;1326;1327;1328</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -3468,7 +3810,7 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
@@ -3477,7 +3819,7 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040203；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3836,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>限时旅券</t>
+          <t>高阶记录盘</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -3510,7 +3852,7 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56｜Task 1341;1342;1343;1344;1345;1346;1347;1348</t>
+          <t>星海手札（二）｜JottingsTask 31;32;33;34;35;36｜Task 1321;1322;1323;1324;1325;1326;1327;1328</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -3519,7 +3861,7 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
@@ -3528,7 +3870,7 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+          <t>DropID 1040203；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
@@ -3545,11 +3887,11 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>2级宝石掉落箱</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="5" t="inlineStr"/>
@@ -3561,7 +3903,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56｜Task 1341;1342;1343;1344;1345;1346;1347;1348</t>
+          <t>星海手札（五）｜JottingsTask 61;62;63;64;65;66;67;68;69;26｜Task 1351;1352;1353;1354;1355;1356;1357;1358;1381;1382;1383;1401</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -3570,21 +3912,892 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040206；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>30级精品装备箱</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（五）｜JottingsTask 61;62;63;64;65;66;67;68;69;26｜Task 1351;1352;1353;1354;1355;1356;1357;1358;1381;1382;1383;1401</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040206；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>收容凭证</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（五）｜JottingsTask 61;62;63;64;65;66;67;68;69;26｜Task 1351;1352;1353;1354;1355;1356;1357;1358;1381;1382;1383;1401</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040206；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>旅券</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（五）｜JottingsTask 61;62;63;64;65;66;67;68;69;26｜Task 1351;1352;1353;1354;1355;1356;1357;1358;1381;1382;1383;1401</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040206；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>未知笔记</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（五）｜JottingsTask 61;62;63;64;65;66;67;68;69;26｜Task 1351;1352;1353;1354;1355;1356;1357;1358;1381;1382;1383;1401</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040206；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>熔晶</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（五）｜JottingsTask 61;62;63;64;65;66;67;68;69;26｜Task 1351;1352;1353;1354;1355;1356;1357;1358;1381;1382;1383;1401</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040206；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>限时旅券</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（五）｜JottingsTask 61;62;63;64;65;66;67;68;69;26｜Task 1351;1352;1353;1354;1355;1356;1357;1358;1381;1382;1383;1401</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040206；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>3级宝石掉落箱</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（六）｜JottingsTask 71;72;73;74;75;76;77;78;79;80｜Task 1361;1362;1363;1364;1365;1366;1367;1368;1384;1385;1386;1387</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040207；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>35级高级装备箱</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（六）｜JottingsTask 71;72;73;74;75;76;77;78;79;80｜Task 1361;1362;1363;1364;1365;1366;1367;1368;1384;1385;1386;1387</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040207；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>史诗能效自选箱</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（六）｜JottingsTask 71;72;73;74;75;76;77;78;79;80｜Task 1361;1362;1363;1364;1365;1366;1367;1368;1384;1385;1386;1387</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040207；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>收容凭证</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（六）｜JottingsTask 71;72;73;74;75;76;77;78;79;80｜Task 1361;1362;1363;1364;1365;1366;1367;1368;1384;1385;1386;1387</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040207；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>旅券</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（六）｜JottingsTask 71;72;73;74;75;76;77;78;79;80｜Task 1361;1362;1363;1364;1365;1366;1367;1368;1384;1385;1386;1387</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040207；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>限时旅券</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（六）｜JottingsTask 71;72;73;74;75;76;77;78;79;80｜Task 1361;1362;1363;1364;1365;1366;1367;1368;1384;1385;1386;1387</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040207；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>25级精品装备箱</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56;57;58｜Task 1341;1342;1343;1344;1345;1346;1347;1348;1349;1350</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>章节任务阶段奖励展开</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>史诗能效自选箱</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56;57;58｜Task 1341;1342;1343;1344;1345;1346;1347;1348;1349;1350</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>指南材料自选箱</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56;57;58｜Task 1341;1342;1343;1344;1345;1346;1347;1348;1349;1350</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>旅券</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56;57;58｜Task 1341;1342;1343;1344;1345;1346;1347;1348;1349;1350</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>正式章节任务阶段奖励</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>限时旅券</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>星海手札（四）｜JottingsTask 51;52;53;54;55;56;57;58｜Task 1341;1342;1343;1344;1345;1346;1347;1348;1349;1350</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>正式:task/Jottings.xlsx + Drop_other.xlsx</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>章节任务阶段奖励展开</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>DropID 1040205；Jottings 阶段奖励，任务链来自 JottingsTask/Task。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M28"/>
+  <autoFilter ref="A1:M45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
